--- a/web/files/港岛-鸭脷洲-凯玥.xlsx
+++ b/web/files/港岛-鸭脷洲-凯玥.xlsx
@@ -1416,7 +1416,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2025-01-12</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2025-01-22</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2025-02-17</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2025-02-16</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -6450,7 +6450,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2023-05-18</t>
+          <t>2023-05-19</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2023-02-13</t>
+          <t>2023-02-14</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2023-01-26</t>
+          <t>2023-01-27</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2023-12-14</t>
+          <t>2023-12-15</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -9490,7 +9490,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -9556,7 +9556,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -9832,7 +9832,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -11158,7 +11158,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2024-01-21</t>
+          <t>2024-01-22</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -12480,7 +12480,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -12682,7 +12682,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -12748,7 +12748,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -12946,7 +12946,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -13012,7 +13012,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -13078,7 +13078,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -13214,7 +13214,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -13350,7 +13350,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -14746,7 +14746,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -14882,7 +14882,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -15018,7 +15018,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -15154,7 +15154,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -15360,7 +15360,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -15426,7 +15426,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -15492,7 +15492,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -15558,7 +15558,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -15690,7 +15690,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -15756,7 +15756,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -15822,7 +15822,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -15888,7 +15888,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -15954,7 +15954,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -16020,7 +16020,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -16086,7 +16086,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -16152,7 +16152,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -16218,7 +16218,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -16284,7 +16284,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -16350,7 +16350,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -16416,7 +16416,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -16482,7 +16482,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -16548,7 +16548,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -16614,7 +16614,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -16680,7 +16680,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -16746,7 +16746,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -16812,7 +16812,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -16878,7 +16878,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -21196,7 +21196,7 @@
           <t>A | 1864呎 (4+房)
 $6080万
 $32,618/呎
-(25年-09月-01日)</t>
+(25年-09月-02日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -21219,7 +21219,7 @@
           <t>A | 1864呎 (4+房)
 $5525万
 $29,642/呎
-(25年-09月-15日)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -21227,7 +21227,7 @@
           <t>B | 2107呎 (4+房)
 $6572万
 $31,191/呎
-(25年-09月-10日)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
     </row>
@@ -21242,7 +21242,7 @@
           <t>A | 1864呎 (4+房)
 $5940万
 $31,866/呎
-(25年-07月-10日)</t>
+(25年-07月-11日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -21273,7 +21273,7 @@
           <t>B | 2107呎 (4+房)
 $6900万
 $32,748/呎
-(24年-08月-20日)</t>
+(24年-08月-21日)</t>
         </is>
       </c>
     </row>
@@ -21288,7 +21288,7 @@
           <t>A | 1864呎 (4+房)
 $5408万
 $29,013/呎
-(25年-07月-10日)</t>
+(25年-07月-11日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -21296,7 +21296,7 @@
           <t>B | 2107呎 (4+房)
 $6600万
 $31,324/呎
-(24年-10月-15日)</t>
+(24年-10月-16日)</t>
         </is>
       </c>
     </row>
@@ -21311,7 +21311,7 @@
           <t>A | 1864呎 (4+房)
 $5800万
 $31,116/呎
-(24年-11月-14日)</t>
+(24年-11月-15日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -21319,7 +21319,7 @@
           <t>B | 2107呎 (4+房)
 $6792万
 $32,234/呎
-(25年-07月-14日)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
     </row>
@@ -21334,7 +21334,7 @@
           <t>A | 1864呎 (4+房)
 $5238万
 $28,101/呎
-(24年-10月-15日)</t>
+(24年-10月-16日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -21342,7 +21342,7 @@
           <t>B | 2107呎 (4+房)
 $6608万
 $31,362/呎
-(24年-09月-09日)</t>
+(24年-09月-10日)</t>
         </is>
       </c>
     </row>
@@ -21357,7 +21357,7 @@
           <t>A | 1864呎 (4+房)
 $5183万
 $27,808/呎
-(24年-07月-16日)</t>
+(24年-07月-17日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -21365,7 +21365,7 @@
           <t>B | 2107呎 (4+房)
 $6446万
 $30,591/呎
-(24年-07月-11日)</t>
+(24年-07月-12日)</t>
         </is>
       </c>
     </row>
@@ -21380,7 +21380,7 @@
           <t>A | 1864呎 (4+房)
 $5561万
 $29,835/呎
-(24年-06月-11日)</t>
+(24年-06月-12日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -21388,7 +21388,7 @@
           <t>B | 2108呎 (4+房)
 $6189万
 $29,358/呎
-(24年-07月-03日)</t>
+(24年-07月-04日)</t>
         </is>
       </c>
     </row>
@@ -21403,7 +21403,7 @@
           <t>A | 1864呎 (4+房)
 $5548万
 $29,765/呎
-(24年-05月-15日)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -21411,7 +21411,7 @@
           <t>B | 2108呎 (4+房)
 $6287万
 $29,825/呎
-(24年-05月-16日)</t>
+(24年-05月-17日)</t>
         </is>
       </c>
     </row>
@@ -21426,7 +21426,7 @@
           <t>A | 1864呎 (4+房)
 $5086万
 $27,283/呎
-(24年-05月-15日)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -21434,7 +21434,7 @@
           <t>B | 2108呎 (4+房)
 $5865万
 $27,821/呎
-(24年-05月-16日)</t>
+(24年-05月-17日)</t>
         </is>
       </c>
     </row>
@@ -21449,7 +21449,7 @@
           <t>A | 1864呎 (4+房)
 $5526万
 $29,645/呎
-(24年-05月-20日)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -21457,7 +21457,7 @@
           <t>B | 2108呎 (4+房)
 $5865万
 $27,821/呎
-(24年-05月-16日)</t>
+(24年-05月-17日)</t>
         </is>
       </c>
     </row>
@@ -21472,7 +21472,7 @@
           <t>A | 1864呎 (4+房)
 $5546万
 $29,756/呎
-(24年-05月-15日)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -21480,7 +21480,7 @@
           <t>B | 2108呎 (4+房)
 $6297万
 $29,873/呎
-(24年-05月-15日)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -21495,7 +21495,7 @@
           <t>A | 1864呎 (4+房)
 $5546万
 $29,756/呎
-(24年-05月-15日)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -21503,7 +21503,7 @@
           <t>B | 2108呎 (4+房)
 $6297万
 $29,873/呎
-(24年-05月-15日)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -21518,7 +21518,7 @@
           <t>A | 1864呎 (4+房)
 $5178万
 $27,778/呎
-(24年-05月-16日)</t>
+(24年-05月-17日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -21526,7 +21526,7 @@
           <t>B | 2108呎 (4+房)
 $6448万
 $30,588/呎
-(24年-05月-16日)</t>
+(24年-05月-17日)</t>
         </is>
       </c>
     </row>
@@ -21541,7 +21541,7 @@
           <t>A | 1864呎 (4+房)
 $4920万
 $26,395/呎
-(24年-07月-11日)</t>
+(24年-07月-12日)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -21549,7 +21549,7 @@
           <t>B | 2108呎 (4+房)
 $6455万
 $30,619/呎
-(24年-05月-15日)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -21564,7 +21564,7 @@
           <t>A | 1864呎 (4+房)
 $5250万
 $28,165/呎
-(25年-02月-19日)</t>
+(25年-02月-20日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -21572,7 +21572,7 @@
           <t>B | 2108呎 (4+房)
 $6046万
 $28,682/呎
-(24年-09月-24日)</t>
+(24年-09月-25日)</t>
         </is>
       </c>
     </row>
@@ -21587,7 +21587,7 @@
           <t>A | 1864呎 (4+房)
 $5380万
 $28,863/呎
-(26年-01月-28日)</t>
+(26年-01月-29日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -21595,7 +21595,7 @@
           <t>B | 2108呎 (4+房)
 $5540万
 $26,281/呎
-(25年-01月-12日)</t>
+(25年-01月-13日)</t>
         </is>
       </c>
     </row>
@@ -21891,7 +21891,7 @@
           <t>A | 2137呎 (4+房)
 $7094万
 $33,196/呎
-(25年-10月-22日)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -21899,7 +21899,7 @@
           <t>B | 2464呎 (4+房)
 $8494万
 $34,472/呎
-(25年-10月-22日)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
     </row>
@@ -21922,7 +21922,7 @@
           <t>B | 2464呎 (4+房)
 $7994万
 $32,444/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
     </row>
@@ -21937,7 +21937,7 @@
           <t>A | 2137呎 (4+房)
 $6582万
 $30,799/呎
-(25年-10月-21日)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -21945,7 +21945,7 @@
           <t>B | 2464呎 (4+房)
 $8200万
 $33,279/呎
-(25年-08月-03日)</t>
+(25年-08月-04日)</t>
         </is>
       </c>
     </row>
@@ -21968,7 +21968,7 @@
           <t>B | 2464呎 (4+房)
 $8200万
 $33,279/呎
-(25年-08月-03日)</t>
+(25年-08月-04日)</t>
         </is>
       </c>
     </row>
@@ -21983,7 +21983,7 @@
           <t>A | 2137呎 (4+房)
 $6526万
 $30,540/呎
-(25年-04月-16日)</t>
+(25年-04月-17日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -21991,7 +21991,7 @@
           <t>B | 2464呎 (4+房)
 $8101万
 $32,876/呎
-(25年-04月-16日)</t>
+(25年-04月-17日)</t>
         </is>
       </c>
     </row>
@@ -22006,7 +22006,7 @@
           <t>A | 2137呎 (4+房)
 $6526万
 $30,540/呎
-(25年-04月-16日)</t>
+(25年-04月-17日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -22014,7 +22014,7 @@
           <t>B | 2464呎 (4+房)
 $8101万
 $32,876/呎
-(25年-04月-16日)</t>
+(25年-04月-17日)</t>
         </is>
       </c>
     </row>
@@ -22029,7 +22029,7 @@
           <t>A | 2137呎 (4+房)
 $6526万
 $30,540/呎
-(25年-04月-16日)</t>
+(25年-04月-17日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -22037,7 +22037,7 @@
           <t>B | 2604呎 (4+房)
 $8101万
 $31,108/呎
-(25年-04月-16日)</t>
+(25年-04月-17日)</t>
         </is>
       </c>
     </row>
@@ -22060,7 +22060,7 @@
           <t>B | 2464呎 (4+房)
 $8333万
 $33,818/呎
-(25年-01月-21日)</t>
+(25年-01月-22日)</t>
         </is>
       </c>
     </row>
@@ -22083,7 +22083,7 @@
           <t>B | 2464呎 (4+房)
 $8122万
 $32,961/呎
-(25年-05月-22日)</t>
+(25年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -22098,7 +22098,7 @@
           <t>A | 2137呎 (4+房)
 $6525万
 $30,536/呎
-(25年-02月-16日)</t>
+(25年-02月-17日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -22106,7 +22106,7 @@
           <t>B | 2464呎 (4+房)
 $8075万
 $32,770/呎
-(25年-02月-17日)</t>
+(25年-02月-18日)</t>
         </is>
       </c>
     </row>
@@ -22121,7 +22121,7 @@
           <t>A | 2137呎 (4+房)
 $6478万
 $30,314/呎
-(25年-09月-29日)</t>
+(25年-09月-30日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -22129,7 +22129,7 @@
           <t>B | 2464呎 (4+房)
 $7900万
 $32,062/呎
-(24年-12月-03日)</t>
+(24年-12月-04日)</t>
         </is>
       </c>
     </row>
@@ -22144,7 +22144,7 @@
           <t>A | 2137呎 (4+房)
 $7163万
 $33,520/呎
-(25年-12月-18日)</t>
+(25年-12月-19日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -22152,7 +22152,7 @@
           <t>B | 2464呎 (4+房)
 $7900万
 $32,062/呎
-(24年-12月-03日)</t>
+(24年-12月-04日)</t>
         </is>
       </c>
     </row>
@@ -22175,7 +22175,7 @@
           <t>B | 2464呎 (4+房)
 $8100万
 $32,873/呎
-(25年-06月-02日)</t>
+(25年-06月-03日)</t>
         </is>
       </c>
     </row>
@@ -22198,7 +22198,7 @@
           <t>B | 2464呎 (4+房)
 $7853万
 $31,870/呎
-(25年-01月-14日)</t>
+(25年-01月-15日)</t>
         </is>
       </c>
     </row>
@@ -22213,7 +22213,7 @@
           <t>A | 2137呎 (4+房)
 $7096万
 $33,206/呎
-(25年-12月-18日)</t>
+(25年-12月-19日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -22221,7 +22221,7 @@
           <t>B | 2464呎 (4+房)
 $8251万
 $33,485/呎
-(25年-12月-18日)</t>
+(25年-12月-19日)</t>
         </is>
       </c>
     </row>
@@ -22236,7 +22236,7 @@
           <t>A | 2137呎 (4+房)
 $6723万
 $31,461/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -22244,7 +22244,7 @@
           <t>B | 2464呎 (4+房)
 $7830万
 $31,776/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
     </row>
@@ -22502,7 +22502,7 @@
           <t>B | 3635呎 (4+房)
 $18466万
 $50,800/呎
-(23年-05月-18日)</t>
+(23年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -22755,7 +22755,7 @@
           <t>B | 3627呎 (4+房)
 $18328万
 $50,531/呎
-(23年-02月-13日)</t>
+(23年-02月-14日)</t>
         </is>
       </c>
     </row>
@@ -22770,7 +22770,7 @@
           <t>A | 3207呎 (4+房)
 $16417万
 $51,191/呎
-(23年-01月-26日)</t>
+(23年-01月-27日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -22778,7 +22778,7 @@
           <t>B | 3477呎 (4+房)
 $14008万
 $40,288/呎
-(26年-05月-03日)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
     </row>
@@ -22801,7 +22801,7 @@
           <t>B | 3477呎 (4+房)
 $17228万
 $49,549/呎
-(23年-12月-14日)</t>
+(23年-12月-15日)</t>
         </is>
       </c>
     </row>
@@ -22816,7 +22816,7 @@
           <t>A | 3207呎 (4+房)
 $12106万
 $37,749/呎
-(24年-07月-17日)</t>
+(24年-07月-18日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -22824,7 +22824,7 @@
           <t>B | 3627呎 (4+房)
 $13194万
 $36,379/呎
-(24年-07月-17日)</t>
+(24年-07月-18日)</t>
         </is>
       </c>
     </row>
@@ -22862,7 +22862,7 @@
           <t>A | 3207呎 (4+房)
 $12066万
 $37,625/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
@@ -23220,7 +23220,7 @@
           <t>B | 1824呎 (4+房)
 $7582万
 $41,566/呎
-(24年-01月-21日)</t>
+(24年-01月-22日)</t>
         </is>
       </c>
     </row>
@@ -23373,7 +23373,7 @@
           <t>A | 2178呎 (4+房)
 $7339万
 $33,695/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -23419,7 +23419,7 @@
           <t>A | 2178呎 (4+房)
 $6745万
 $30,970/呎
-(25年-08月-11日)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -23442,7 +23442,7 @@
           <t>A | 2178呎 (4+房)
 $7251万
 $33,290/呎
-(24年-11月-03日)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -23465,7 +23465,7 @@
           <t>A | 2178呎 (4+房)
 $6956万
 $31,937/呎
-(25年-10月-01日)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -23473,7 +23473,7 @@
           <t>B | 1824呎 (4+房)
 $5323万
 $29,181/呎
-(25年-10月-01日)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
     </row>
@@ -23488,7 +23488,7 @@
           <t>A | 2178呎 (4+房)
 $6468万
 $29,697/呎
-(24年-07月-03日)</t>
+(24年-07月-04日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -23496,7 +23496,7 @@
           <t>B | 1824呎 (4+房)
 $5800万
 $31,798/呎
-(24年-05月-16日)</t>
+(24年-05月-17日)</t>
         </is>
       </c>
     </row>
@@ -23511,7 +23511,7 @@
           <t>A | 2178呎 (4+房)
 $6280万
 $28,834/呎
-(25年-07月-28日)</t>
+(25年-07月-29日)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -23519,7 +23519,7 @@
           <t>B | 1944呎 (4+房)
 $6318万
 $32,500/呎
-(26年-07月-14日)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
     </row>
@@ -23542,7 +23542,7 @@
           <t>B | 1824呎 (4+房)
 $5724万
 $31,379/呎
-(26年-02月-01日)</t>
+(26年-02月-02日)</t>
         </is>
       </c>
     </row>
@@ -23565,7 +23565,7 @@
           <t>B | 1824呎 (4+房)
 $5953万
 $32,634/呎
-(26年-06月-23日)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
     </row>
@@ -23588,7 +23588,7 @@
           <t>B | 1824呎 (4+房)
 $5724万
 $31,379/呎
-(26年-03月-02日)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
     </row>
@@ -23914,7 +23914,7 @@
           <t>A | 1626呎 (4+房)
 $4910万
 $30,197/呎
-(25年-09月-14日)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -23937,7 +23937,7 @@
           <t>A | 1626呎 (4+房)
 $4768万
 $29,323/呎
-(25年-05月-28日)</t>
+(25年-05月-29日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -23960,7 +23960,7 @@
           <t>A | 1626呎 (4+房)
 $4768万
 $29,323/呎
-(25年-06月-01日)</t>
+(25年-06月-02日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -23983,7 +23983,7 @@
           <t>A | 1626呎 (4+房)
 $4378万
 $26,927/呎
-(25年-06月-18日)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -24029,7 +24029,7 @@
           <t>A | 1626呎 (4+房)
 $4242万
 $26,092/呎
-(25年-05月-14日)</t>
+(25年-05月-15日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -24037,7 +24037,7 @@
           <t>B | 1619呎 (4+房)
 $4206万
 $25,977/呎
-(25年-07月-01日)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
     </row>
@@ -24052,7 +24052,7 @@
           <t>A | 1626呎 (4+房)
 $4209万
 $25,883/呎
-(25年-05月-07日)</t>
+(25年-05月-08日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -24060,7 +24060,7 @@
           <t>B | 1619呎 (4+房)
 $4189万
 $25,872/呎
-(25年-06月-02日)</t>
+(25年-06月-03日)</t>
         </is>
       </c>
     </row>
@@ -24075,7 +24075,7 @@
           <t>A | 1626呎 (4+房)
 $4124万
 $25,361/呎
-(24年-06月-27日)</t>
+(24年-06月-28日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -24083,7 +24083,7 @@
           <t>B | 1619呎 (4+房)
 $4504万
 $27,821/呎
-(24年-06月-27日)</t>
+(24年-06月-28日)</t>
         </is>
       </c>
     </row>
@@ -24098,7 +24098,7 @@
           <t>A | 1626呎 (4+房)
 $4592万
 $28,239/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -24106,7 +24106,7 @@
           <t>B | 1619呎 (4+房)
 $4172万
 $25,768/呎
-(25年-02月-18日)</t>
+(25年-02月-19日)</t>
         </is>
       </c>
     </row>
@@ -24121,7 +24121,7 @@
           <t>A | 1626呎 (4+房)
 $4158万
 $25,570/呎
-(24年-10月-30日)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -24129,7 +24129,7 @@
           <t>B | 1619呎 (4+房)
 $4155万
 $25,664/呎
-(24年-11月-10日)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -24144,7 +24144,7 @@
           <t>A | 1626呎 (4+房)
 $4200万
 $25,830/呎
-(24年-12月-17日)</t>
+(24年-12月-18日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -24152,7 +24152,7 @@
           <t>B | 1619呎 (4+房)
 $4238万
 $26,177/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
     </row>
@@ -24167,7 +24167,7 @@
           <t>A | 1626呎 (4+房)
 $4158万
 $25,570/呎
-(24年-11月-21日)</t>
+(24年-11月-22日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -24175,7 +24175,7 @@
           <t>B | 1619呎 (4+房)
 $4200万
 $25,942/呎
-(25年-10月-05日)</t>
+(25年-10月-06日)</t>
         </is>
       </c>
     </row>
@@ -24190,7 +24190,7 @@
           <t>A | 1626呎 (4+房)
 $4141万
 $25,465/呎
-(24年-07月-16日)</t>
+(24年-07月-17日)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -24198,7 +24198,7 @@
           <t>B | 1619呎 (4+房)
 $4316万
 $26,660/呎
-(25年-12月-03日)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
     </row>
@@ -24213,7 +24213,7 @@
           <t>A | 1626呎 (4+房)
 $4523万
 $27,815/呎
-(24年-10月-30日)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -24221,7 +24221,7 @@
           <t>B | 1619呎 (4+房)
 $4150万
 $25,633/呎
-(25年-10月-29日)</t>
+(25年-10月-30日)</t>
         </is>
       </c>
     </row>
@@ -24236,7 +24236,7 @@
           <t>A | 1626呎 (4+房)
 $4163万
 $25,601/呎
-(25年-07月-01日)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -24244,7 +24244,7 @@
           <t>B | 1619呎 (4+房)
 $4750万
 $29,339/呎
-(25年-12月-10日)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
     </row>
@@ -24259,7 +24259,7 @@
           <t>A | 1626呎 (4+房)
 $4209万
 $25,883/呎
-(25年-05月-29日)</t>
+(25年-05月-30日)</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
@@ -24267,7 +24267,7 @@
           <t>B | 1619呎 (4+房)
 $4273万
 $26,394/呎
-(25年-12月-17日)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
     </row>
@@ -24282,7 +24282,7 @@
           <t>A | 1626呎 (4+房)
 $4327万
 $26,613/呎
-(25年-12月-10日)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
@@ -24290,7 +24290,7 @@
           <t>B | 1619呎 (4+房)
 $4950万
 $30,574/呎
-(26年-02月-09日)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-鸭脷洲-凯玥.xlsx
+++ b/web/files/港岛-鸭脷洲-凯玥.xlsx
@@ -12937,7 +12937,7 @@
         </is>
       </c>
       <c r="E181" s="4" t="n">
-        <v>1944</v>
+        <v>1824</v>
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
@@ -12946,14 +12946,14 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
         <v>63180000</v>
       </c>
       <c r="I181" s="5" t="n">
-        <v>32500</v>
+        <v>34638</v>
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
       </c>
       <c r="F286" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G286" s="3" t="inlineStr">
@@ -20169,12 +20169,12 @@
       </c>
       <c r="H286" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I286" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J286" s="3" t="inlineStr">
@@ -20184,12 +20184,12 @@
       </c>
       <c r="K286" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L286" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M286" s="3" t="inlineStr">
@@ -20199,7 +20199,7 @@
       </c>
       <c r="N286" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -20229,7 +20229,7 @@
       </c>
       <c r="F287" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
@@ -20239,12 +20239,12 @@
       </c>
       <c r="H287" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I287" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J287" s="3" t="inlineStr">
@@ -20254,12 +20254,12 @@
       </c>
       <c r="K287" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L287" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M287" s="3" t="inlineStr">
@@ -20269,7 +20269,7 @@
       </c>
       <c r="N287" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -20299,7 +20299,7 @@
       </c>
       <c r="F288" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G288" s="3" t="inlineStr">
@@ -20309,12 +20309,12 @@
       </c>
       <c r="H288" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I288" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J288" s="3" t="inlineStr">
@@ -20324,12 +20324,12 @@
       </c>
       <c r="K288" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L288" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M288" s="3" t="inlineStr">
@@ -20339,7 +20339,7 @@
       </c>
       <c r="N288" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -20369,7 +20369,7 @@
       </c>
       <c r="F289" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G289" s="3" t="inlineStr">
@@ -20379,12 +20379,12 @@
       </c>
       <c r="H289" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I289" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J289" s="3" t="inlineStr">
@@ -20394,12 +20394,12 @@
       </c>
       <c r="K289" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L289" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M289" s="3" t="inlineStr">
@@ -20409,7 +20409,7 @@
       </c>
       <c r="N289" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -20439,7 +20439,7 @@
       </c>
       <c r="F290" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G290" s="3" t="inlineStr">
@@ -20449,12 +20449,12 @@
       </c>
       <c r="H290" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I290" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J290" s="3" t="inlineStr">
@@ -20464,12 +20464,12 @@
       </c>
       <c r="K290" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L290" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M290" s="3" t="inlineStr">
@@ -20479,7 +20479,7 @@
       </c>
       <c r="N290" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -20509,7 +20509,7 @@
       </c>
       <c r="F291" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G291" s="3" t="inlineStr">
@@ -20519,12 +20519,12 @@
       </c>
       <c r="H291" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I291" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J291" s="3" t="inlineStr">
@@ -20534,12 +20534,12 @@
       </c>
       <c r="K291" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L291" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M291" s="3" t="inlineStr">
@@ -20549,7 +20549,7 @@
       </c>
       <c r="N291" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -20579,7 +20579,7 @@
       </c>
       <c r="F292" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G292" s="3" t="inlineStr">
@@ -20589,12 +20589,12 @@
       </c>
       <c r="H292" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I292" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J292" s="3" t="inlineStr">
@@ -20604,12 +20604,12 @@
       </c>
       <c r="K292" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L292" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M292" s="3" t="inlineStr">
@@ -20619,7 +20619,7 @@
       </c>
       <c r="N292" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -20649,7 +20649,7 @@
       </c>
       <c r="F293" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G293" s="3" t="inlineStr">
@@ -20659,12 +20659,12 @@
       </c>
       <c r="H293" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I293" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J293" s="3" t="inlineStr">
@@ -20674,12 +20674,12 @@
       </c>
       <c r="K293" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L293" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M293" s="3" t="inlineStr">
@@ -20689,7 +20689,7 @@
       </c>
       <c r="N293" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -20719,7 +20719,7 @@
       </c>
       <c r="F294" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G294" s="3" t="inlineStr">
@@ -20729,12 +20729,12 @@
       </c>
       <c r="H294" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I294" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J294" s="3" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="K294" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L294" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M294" s="3" t="inlineStr">
@@ -20759,7 +20759,7 @@
       </c>
       <c r="N294" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -20789,7 +20789,7 @@
       </c>
       <c r="F295" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G295" s="3" t="inlineStr">
@@ -20799,12 +20799,12 @@
       </c>
       <c r="H295" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I295" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J295" s="3" t="inlineStr">
@@ -20814,12 +20814,12 @@
       </c>
       <c r="K295" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L295" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M295" s="3" t="inlineStr">
@@ -20829,7 +20829,7 @@
       </c>
       <c r="N295" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -23516,10 +23516,10 @@
       </c>
       <c r="C25" s="23" t="inlineStr">
         <is>
-          <t>B | 1944呎 (4+房)
+          <t>B | 1824呎 (4+房)
 $6318万
-$32,500/呎
-(26年-07月-15日)</t>
+$34,638/呎
+(26年-08月-11日)</t>
         </is>
       </c>
     </row>
@@ -24387,27 +24387,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>46</t>
         </is>
       </c>
     </row>
@@ -24940,20 +24940,20 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B27" s="20" t="inlineStr">
+      <c r="B27" s="24" t="inlineStr">
         <is>
           <t>A | 1393呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C27" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
         <is>
           <t>B | 1393呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -24963,20 +24963,20 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B28" s="20" t="inlineStr">
+      <c r="B28" s="24" t="inlineStr">
         <is>
           <t>A | 1393呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C28" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
         <is>
           <t>B | 1393呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -24986,20 +24986,20 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B29" s="20" t="inlineStr">
+      <c r="B29" s="24" t="inlineStr">
         <is>
           <t>A | 1393呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C29" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
         <is>
           <t>B | 1393呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -25009,20 +25009,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B30" s="20" t="inlineStr">
+      <c r="B30" s="24" t="inlineStr">
         <is>
           <t>A | 1393呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C30" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
         <is>
           <t>B | 1393呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -25032,20 +25032,20 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B31" s="20" t="inlineStr">
+      <c r="B31" s="24" t="inlineStr">
         <is>
           <t>A | 1393呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C31" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
         <is>
           <t>B | 1393呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-鸭脷洲-凯玥.xlsx
+++ b/web/files/港岛-鸭脷洲-凯玥.xlsx
@@ -20159,23 +20159,19 @@
       </c>
       <c r="F286" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H286" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I286" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="H286" s="5" t="n">
+        <v>36000000</v>
+      </c>
+      <c r="I286" s="5" t="n">
+        <v>25844</v>
       </c>
       <c r="J286" s="3" t="inlineStr">
         <is>
@@ -20184,12 +20180,12 @@
       </c>
       <c r="K286" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L286" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M286" s="3" t="inlineStr">
@@ -20199,7 +20195,7 @@
       </c>
       <c r="N286" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -24387,7 +24383,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -24397,7 +24393,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -24948,12 +24944,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C27" s="24" t="inlineStr">
+      <c r="C27" s="23" t="inlineStr">
         <is>
           <t>B | 1393呎 (3房)
-招标单位
--
-(在售)</t>
+$3600万
+$25,844/呎
+(26年-08月-16日)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-鸭脷洲-凯玥.xlsx
+++ b/web/files/港岛-鸭脷洲-凯玥.xlsx
@@ -20295,23 +20295,19 @@
       </c>
       <c r="F288" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H288" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I288" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="H288" s="5" t="n">
+        <v>35350000</v>
+      </c>
+      <c r="I288" s="5" t="n">
+        <v>25377</v>
       </c>
       <c r="J288" s="3" t="inlineStr">
         <is>
@@ -20320,12 +20316,12 @@
       </c>
       <c r="K288" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L288" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M288" s="3" t="inlineStr">
@@ -20335,7 +20331,7 @@
       </c>
       <c r="N288" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -24383,7 +24379,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -24393,7 +24389,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -24967,12 +24963,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C28" s="24" t="inlineStr">
+      <c r="C28" s="23" t="inlineStr">
         <is>
           <t>B | 1393呎 (3房)
-招标单位
--
-(在售)</t>
+$3535万
+$25,377/呎
+(26年-08月-28日)</t>
         </is>
       </c>
     </row>
